--- a/data/trans_dic/IMC_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,81; 66,87</t>
+          <t>59,35; 66,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,93; 73,89</t>
+          <t>66,95; 74,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,18; 68,67</t>
+          <t>60,85; 68,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,54; 72,88</t>
+          <t>64,66; 72,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,45; 55,66</t>
+          <t>48,57; 56,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,64; 58,73</t>
+          <t>51,02; 58,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,57; 58,58</t>
+          <t>50,46; 58,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,02; 59,48</t>
+          <t>52,85; 59,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,21; 60,49</t>
+          <t>55,18; 60,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,24; 65,36</t>
+          <t>60,22; 65,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,17; 62,41</t>
+          <t>57,12; 62,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,81; 65,07</t>
+          <t>59,64; 65,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,8; 65,17</t>
+          <t>58,45; 65,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,13; 69,04</t>
+          <t>62,67; 69,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,43; 62,67</t>
+          <t>56,33; 62,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,98; 81,52</t>
+          <t>57,54; 83,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,34; 52,75</t>
+          <t>46,38; 52,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,64; 59,04</t>
+          <t>52,51; 59,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,76; 58,77</t>
+          <t>52,45; 59,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,17; 53,71</t>
+          <t>48,29; 53,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,73; 58,32</t>
+          <t>53,76; 58,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,67; 63,31</t>
+          <t>58,73; 63,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,34; 60,03</t>
+          <t>55,39; 60,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,25; 72,5</t>
+          <t>53,98; 73,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,92; 59,86</t>
+          <t>52,1; 59,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,48; 63,96</t>
+          <t>56,09; 63,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,68; 63,08</t>
+          <t>55,64; 62,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,19; 65,87</t>
+          <t>57,42; 66,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,0; 49,41</t>
+          <t>42,29; 49,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,77; 60,42</t>
+          <t>52,84; 60,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,12; 50,85</t>
+          <t>43,83; 51,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,86; 81,36</t>
+          <t>48,04; 79,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,09; 53,53</t>
+          <t>48,18; 53,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,65; 60,87</t>
+          <t>55,24; 60,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,43; 55,88</t>
+          <t>50,86; 56,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,56; 75,46</t>
+          <t>54,62; 75,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,84; 59,47</t>
+          <t>52,77; 59,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,29; 68,21</t>
+          <t>62,39; 68,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,75; 63,41</t>
+          <t>56,4; 63,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,48; 65,55</t>
+          <t>58,17; 65,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,73; 45,87</t>
+          <t>39,8; 45,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,78; 54,17</t>
+          <t>47,71; 53,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,85; 54,56</t>
+          <t>47,91; 54,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,96; 63,46</t>
+          <t>48,85; 62,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,5; 51,18</t>
+          <t>46,68; 51,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,44; 60,04</t>
+          <t>55,51; 60,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,03; 57,6</t>
+          <t>52,74; 57,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,43; 62,05</t>
+          <t>54,51; 62,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,66; 61,05</t>
+          <t>57,54; 61,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,66; 67,09</t>
+          <t>63,67; 67,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,13; 62,53</t>
+          <t>59,01; 62,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61,42; 73,38</t>
+          <t>61,45; 72,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,43; 49,1</t>
+          <t>45,47; 48,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 56,01</t>
+          <t>52,54; 56,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,56; 54,04</t>
+          <t>50,48; 54,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,31; 63,51</t>
+          <t>51,6; 63,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,82; 54,35</t>
+          <t>51,98; 54,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,58; 61,05</t>
+          <t>58,7; 61,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55,26; 57,7</t>
+          <t>55,08; 57,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,11; 65,2</t>
+          <t>57,2; 65,83</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>412267; 460950</t>
+          <t>409117; 460166</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>464235; 512518</t>
+          <t>464377; 513646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>390550; 438382</t>
+          <t>388426; 438732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>400493; 452224</t>
+          <t>401234; 452516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>328989; 377929</t>
+          <t>329822; 380976</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>335342; 388872</t>
+          <t>337816; 389869</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>311414; 360758</t>
+          <t>310774; 359406</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>342061; 383734</t>
+          <t>340965; 384098</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755522; 827687</t>
+          <t>755123; 828122</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>816717; 886135</t>
+          <t>816386; 891366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>717033; 782742</t>
+          <t>716375; 785458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>756977; 823574</t>
+          <t>754845; 823550</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>560810; 621553</t>
+          <t>557452; 623450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>626192; 684766</t>
+          <t>621591; 686079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>555415; 616785</t>
+          <t>554439; 616344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>673639; 963710</t>
+          <t>680262; 989692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>442877; 504115</t>
+          <t>443250; 505959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>520598; 583906</t>
+          <t>519347; 583791</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>524533; 584342</t>
+          <t>521421; 587104</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>446791; 498176</t>
+          <t>447915; 499819</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1025919; 1113541</t>
+          <t>1026479; 1110804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1162070; 1254090</t>
+          <t>1163427; 1257360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1094923; 1187609</t>
+          <t>1095795; 1189186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1144439; 1529463</t>
+          <t>1138808; 1550703</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>348950; 402309</t>
+          <t>350151; 402388</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>417910; 473280</t>
+          <t>415022; 472188</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415124; 470278</t>
+          <t>414847; 469292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>398569; 459010</t>
+          <t>400178; 462901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>284413; 334563</t>
+          <t>286373; 336944</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>393484; 450476</t>
+          <t>394012; 450872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>322334; 380080</t>
+          <t>327622; 383547</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>420258; 714432</t>
+          <t>421811; 697261</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>648852; 722330</t>
+          <t>650100; 726726</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>826714; 904231</t>
+          <t>820670; 903136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>752886; 834296</t>
+          <t>759381; 838428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>859285; 1188516</t>
+          <t>860281; 1186292</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>490836; 552473</t>
+          <t>490184; 548546</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>582356; 637736</t>
+          <t>583299; 641167</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>514022; 574318</t>
+          <t>510861; 572743</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>525503; 589063</t>
+          <t>522771; 591394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>405671; 468385</t>
+          <t>406344; 468224</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>482956; 547580</t>
+          <t>482257; 545675</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>471185; 537317</t>
+          <t>471819; 536831</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>513760; 665986</t>
+          <t>512695; 659992</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>906832; 998087</t>
+          <t>910223; 1000743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1078652; 1168159</t>
+          <t>1080018; 1169885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1002563; 1089026</t>
+          <t>997158; 1089164</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1060327; 1208715</t>
+          <t>1061949; 1211520</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1870667; 1980387</t>
+          <t>1866586; 1979827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2139359; 2254473</t>
+          <t>2139579; 2253686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1935748; 2047170</t>
+          <t>1932044; 2043113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2087287; 2493642</t>
+          <t>2088119; 2474728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1514167; 1636648</t>
+          <t>1515368; 1632779</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1791319; 1908600</t>
+          <t>1790187; 1912198</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1690039; 1806197</t>
+          <t>1687084; 1809568</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1795803; 2223087</t>
+          <t>1806140; 2215162</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3408281; 3574539</t>
+          <t>3418548; 3579984</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3964416; 4131460</t>
+          <t>3972883; 4136184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656367; 3817441</t>
+          <t>3644058; 3813354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3939613; 4497479</t>
+          <t>3946098; 4540917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 66,76</t>
+          <t>59,23; 66,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,95; 74,05</t>
+          <t>66,96; 74,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,85; 68,73</t>
+          <t>61,17; 68,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,66; 72,92</t>
+          <t>63,78; 71,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,57; 56,1</t>
+          <t>48,36; 55,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,02; 58,88</t>
+          <t>50,4; 58,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,46; 58,36</t>
+          <t>50,53; 58,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,85; 59,54</t>
+          <t>52,58; 59,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,18; 60,52</t>
+          <t>55,02; 60,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,22; 65,75</t>
+          <t>59,82; 65,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,12; 62,63</t>
+          <t>57,12; 62,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,64; 65,07</t>
+          <t>59,08; 64,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,45; 65,37</t>
+          <t>58,93; 65,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,67; 69,17</t>
+          <t>62,96; 69,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,33; 62,62</t>
+          <t>56,64; 62,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,54; 83,72</t>
+          <t>54,56; 61,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,38; 52,94</t>
+          <t>46,3; 52,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,51; 59,03</t>
+          <t>52,48; 59,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,45; 59,05</t>
+          <t>52,67; 58,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,29; 53,89</t>
+          <t>48,78; 54,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,76; 58,18</t>
+          <t>53,23; 58,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,73; 63,48</t>
+          <t>58,67; 63,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,39; 60,11</t>
+          <t>55,44; 59,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,98; 73,5</t>
+          <t>52,81; 57,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,1; 59,87</t>
+          <t>51,76; 59,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,09; 63,81</t>
+          <t>55,8; 63,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,64; 62,95</t>
+          <t>55,38; 63,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,42; 66,43</t>
+          <t>58,98; 66,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,29; 49,76</t>
+          <t>42,47; 49,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,84; 60,47</t>
+          <t>52,51; 60,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,83; 51,31</t>
+          <t>43,63; 51,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,04; 79,41</t>
+          <t>46,46; 53,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,18; 53,86</t>
+          <t>47,98; 53,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55,24; 60,79</t>
+          <t>55,57; 60,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,86; 56,16</t>
+          <t>50,82; 55,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54,62; 75,32</t>
+          <t>53,62; 58,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,77; 59,05</t>
+          <t>52,56; 59,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,39; 68,58</t>
+          <t>62,1; 68,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,4; 63,23</t>
+          <t>56,85; 63,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,17; 65,81</t>
+          <t>57,49; 64,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,8; 45,86</t>
+          <t>39,35; 45,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,71; 53,98</t>
+          <t>47,79; 54,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,91; 54,51</t>
+          <t>47,57; 54,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,85; 62,89</t>
+          <t>47,62; 52,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,68; 51,32</t>
+          <t>46,72; 51,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,51; 60,13</t>
+          <t>55,51; 60,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,74; 57,61</t>
+          <t>53,3; 57,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,51; 62,19</t>
+          <t>53,2; 57,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,54; 61,03</t>
+          <t>57,64; 61,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,67; 67,07</t>
+          <t>63,75; 67,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,01; 62,41</t>
+          <t>58,94; 62,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61,45; 72,82</t>
+          <t>60,13; 63,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,47; 48,99</t>
+          <t>45,59; 48,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,54; 56,12</t>
+          <t>52,6; 56,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,48; 54,14</t>
+          <t>50,49; 53,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,6; 63,29</t>
+          <t>50,07; 53,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,98; 54,43</t>
+          <t>52,04; 54,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,7; 61,11</t>
+          <t>58,52; 61,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55,08; 57,64</t>
+          <t>55,19; 57,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,2; 65,83</t>
+          <t>55,53; 57,89</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427462</t>
+          <t>451616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>362505</t>
+          <t>390210</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>789967</t>
+          <t>841826</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>409117; 460166</t>
+          <t>408311; 459396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>464377; 513646</t>
+          <t>464465; 513290</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388426; 438732</t>
+          <t>390464; 438770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>401234; 452516</t>
+          <t>426072; 476319</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>329822; 380976</t>
+          <t>328379; 379900</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>337816; 389869</t>
+          <t>333734; 388324</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>310774; 359406</t>
+          <t>311151; 359430</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>340965; 384098</t>
+          <t>366601; 412222</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755123; 828122</t>
+          <t>752918; 825751</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>816386; 891366</t>
+          <t>811075; 883100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>716375; 785458</t>
+          <t>716351; 781699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>754845; 823550</t>
+          <t>806504; 877315</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>791776</t>
+          <t>605823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>473813</t>
+          <t>535958</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1265589</t>
+          <t>1141781</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>557452; 623450</t>
+          <t>562050; 624994</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>621591; 686079</t>
+          <t>624487; 685774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>554439; 616344</t>
+          <t>557460; 617934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>680262; 989692</t>
+          <t>566076; 639903</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>443250; 505959</t>
+          <t>442440; 503719</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>519347; 583791</t>
+          <t>519006; 584344</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>521421; 587104</t>
+          <t>523613; 584002</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>447915; 499819</t>
+          <t>506114; 564210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1026479; 1110804</t>
+          <t>1016439; 1109894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1163427; 1257360</t>
+          <t>1162112; 1255725</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1095795; 1189186</t>
+          <t>1096840; 1186138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1138808; 1550703</t>
+          <t>1095722; 1192708</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432510</t>
+          <t>495388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>534265</t>
+          <t>391025</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>966776</t>
+          <t>886412</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>350151; 402388</t>
+          <t>347877; 402979</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415022; 472188</t>
+          <t>412904; 470387</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>414847; 469292</t>
+          <t>412877; 469980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>400178; 462901</t>
+          <t>464878; 526327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>286373; 336944</t>
+          <t>287570; 337160</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>394012; 450872</t>
+          <t>391483; 449513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>327622; 383547</t>
+          <t>326145; 382511</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>421811; 697261</t>
+          <t>365885; 418599</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>650100; 726726</t>
+          <t>647415; 721580</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>820670; 903136</t>
+          <t>825558; 904364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>759381; 838428</t>
+          <t>758804; 835952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>860281; 1186292</t>
+          <t>844934; 927853</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556334</t>
+          <t>585544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>558436</t>
+          <t>537062</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1114771</t>
+          <t>1122606</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>490184; 548546</t>
+          <t>488221; 549320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>583299; 641167</t>
+          <t>580554; 637682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>510861; 572743</t>
+          <t>514937; 575999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>522771; 591394</t>
+          <t>551085; 617935</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>406344; 468224</t>
+          <t>401810; 465358</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>482257; 545675</t>
+          <t>483050; 546356</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>471819; 536831</t>
+          <t>468499; 531819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>512695; 659992</t>
+          <t>509618; 566326</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>910223; 1000743</t>
+          <t>911052; 999548</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1080018; 1169885</t>
+          <t>1080139; 1169016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>997158; 1089164</t>
+          <t>1007746; 1093009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1061949; 1211520</t>
+          <t>1079271; 1167263</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1866586; 1979827</t>
+          <t>1869898; 1981608</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2139579; 2253686</t>
+          <t>2142227; 2257017</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1932044; 2043113</t>
+          <t>1929506; 2045342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2088119; 2474728</t>
+          <t>2075818; 2201794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1515368; 1632779</t>
+          <t>1519462; 1631473</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1790187; 1912198</t>
+          <t>1792324; 1914143</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1687084; 1809568</t>
+          <t>1687468; 1800615</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1806140; 2215162</t>
+          <t>1798777; 1905633</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3418548; 3579984</t>
+          <t>3422415; 3589263</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3972883; 4136184</t>
+          <t>3960643; 4128547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3644058; 3813354</t>
+          <t>3651727; 3812538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3946098; 4540917</t>
+          <t>3911796; 4078433</t>
         </is>
       </c>
     </row>
